--- a/서버정보/20260911_리소스배포_테스트.xlsx
+++ b/서버정보/20260911_리소스배포_테스트.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\zenithn\PowerShell - 리소스 배포\서버정보\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B9C9E703-F4AE-4E61-BC78-90B575BD9614}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{705B20C8-B990-4860-91B9-03F8563A8324}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="9" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="VNET" sheetId="4" r:id="rId1"/>
@@ -1659,7 +1659,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4207" uniqueCount="610">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4207" uniqueCount="607">
   <si>
     <t>Stage</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -3818,17 +3818,6 @@
   </si>
   <si>
     <t>10.157.144.161</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>hazr-t-dis-ext-vnet</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>hazr-t-dis-int-vnet</t>
-  </si>
-  <si>
-    <t>hazr-t-dis-int-vnet</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -4383,7 +4372,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="119">
+  <cellXfs count="115">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -4726,20 +4715,8 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1">
-      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -10303,7 +10280,7 @@
         <v>286</v>
       </c>
       <c r="D60" s="84" t="s">
-        <v>599</v>
+        <v>596</v>
       </c>
       <c r="E60" s="84" t="str">
         <f t="shared" si="24"/>
@@ -10364,7 +10341,7 @@
         <v>286</v>
       </c>
       <c r="D61" s="74" t="s">
-        <v>601</v>
+        <v>598</v>
       </c>
       <c r="E61" s="74" t="str">
         <f t="shared" si="28"/>
@@ -10425,7 +10402,7 @@
         <v>286</v>
       </c>
       <c r="D62" s="84" t="s">
-        <v>603</v>
+        <v>600</v>
       </c>
       <c r="E62" s="84" t="str">
         <f t="shared" si="24"/>
@@ -10486,7 +10463,7 @@
         <v>286</v>
       </c>
       <c r="D63" s="74" t="s">
-        <v>605</v>
+        <v>602</v>
       </c>
       <c r="E63" s="74" t="str">
         <f t="shared" si="28"/>
@@ -10547,7 +10524,7 @@
         <v>286</v>
       </c>
       <c r="D64" s="84" t="s">
-        <v>607</v>
+        <v>604</v>
       </c>
       <c r="E64" s="84" t="str">
         <f t="shared" si="24"/>
@@ -15928,7 +15905,7 @@
         <f t="array" ref="C58">UPPER(INDEX(_xlfn.TEXTSPLIT($D58, "-"), 3))</f>
         <v>DIS</v>
       </c>
-      <c r="D58" s="114" t="s">
+      <c r="D58" s="107" t="s">
         <v>577</v>
       </c>
       <c r="E58" s="107" t="s">
@@ -15961,7 +15938,7 @@
       <c r="N58" s="110" t="s">
         <v>584</v>
       </c>
-      <c r="O58" s="114" t="str">
+      <c r="O58" s="107" t="str">
         <f t="shared" ref="O58:O62" si="8">SUBSTITUTE(F58,"hazr-","")&amp;"-osdisk"</f>
         <v>t-dis-clvweb01-osdisk</v>
       </c>
@@ -15971,10 +15948,10 @@
       <c r="Q58" s="107" t="s">
         <v>181</v>
       </c>
-      <c r="R58" s="114"/>
+      <c r="R58" s="107"/>
       <c r="S58" s="107"/>
-      <c r="T58" s="114"/>
-      <c r="U58" s="114" t="str">
+      <c r="T58" s="107"/>
+      <c r="U58" s="107" t="str">
         <f t="shared" ref="U58:U62" si="9">SUBSTITUTE(F58,"hazr-","")&amp;"-nic"</f>
         <v>t-dis-clvweb01-nic</v>
       </c>
@@ -15988,10 +15965,10 @@
         <v>198</v>
       </c>
       <c r="Y58" s="107" t="s">
+        <v>451</v>
+      </c>
+      <c r="Z58" s="107" t="s">
         <v>589</v>
-      </c>
-      <c r="Z58" s="107" t="s">
-        <v>592</v>
       </c>
       <c r="AA58" s="107" t="b">
         <v>1</v>
@@ -16016,7 +15993,7 @@
         <f t="array" ref="C59">UPPER(INDEX(_xlfn.TEXTSPLIT($D59, "-"), 3))</f>
         <v>DIS</v>
       </c>
-      <c r="D59" s="115" t="s">
+      <c r="D59" s="113" t="s">
         <v>577</v>
       </c>
       <c r="E59" s="113" t="s">
@@ -16028,7 +16005,7 @@
       <c r="G59" s="113" t="s">
         <v>585</v>
       </c>
-      <c r="H59" s="116" t="s">
+      <c r="H59" s="114" t="s">
         <v>179</v>
       </c>
       <c r="I59" s="113">
@@ -16049,7 +16026,7 @@
       <c r="N59" s="110" t="s">
         <v>584</v>
       </c>
-      <c r="O59" s="115" t="str">
+      <c r="O59" s="113" t="str">
         <f t="shared" si="8"/>
         <v>t-dis-clvap01-osdisk</v>
       </c>
@@ -16059,10 +16036,10 @@
       <c r="Q59" s="107" t="s">
         <v>181</v>
       </c>
-      <c r="R59" s="115"/>
+      <c r="R59" s="113"/>
       <c r="S59" s="113"/>
-      <c r="T59" s="115"/>
-      <c r="U59" s="115" t="str">
+      <c r="T59" s="113"/>
+      <c r="U59" s="113" t="str">
         <f t="shared" si="9"/>
         <v>t-dis-clvap01-nic</v>
       </c>
@@ -16076,10 +16053,10 @@
         <v>198</v>
       </c>
       <c r="Y59" s="113" t="s">
-        <v>591</v>
+        <v>450</v>
       </c>
       <c r="Z59" s="113" t="s">
-        <v>593</v>
+        <v>590</v>
       </c>
       <c r="AA59" s="107" t="b">
         <v>1</v>
@@ -16104,7 +16081,7 @@
         <f t="array" ref="C60">UPPER(INDEX(_xlfn.TEXTSPLIT($D60, "-"), 3))</f>
         <v>DIS</v>
       </c>
-      <c r="D60" s="114" t="s">
+      <c r="D60" s="107" t="s">
         <v>577</v>
       </c>
       <c r="E60" s="113" t="s">
@@ -16116,7 +16093,7 @@
       <c r="G60" s="113" t="s">
         <v>586</v>
       </c>
-      <c r="H60" s="116" t="s">
+      <c r="H60" s="114" t="s">
         <v>179</v>
       </c>
       <c r="I60" s="107">
@@ -16137,7 +16114,7 @@
       <c r="N60" s="110" t="s">
         <v>584</v>
       </c>
-      <c r="O60" s="115" t="str">
+      <c r="O60" s="113" t="str">
         <f t="shared" si="8"/>
         <v>t-dis-clvssrap01-osdisk</v>
       </c>
@@ -16147,10 +16124,10 @@
       <c r="Q60" s="107" t="s">
         <v>181</v>
       </c>
-      <c r="R60" s="115"/>
+      <c r="R60" s="113"/>
       <c r="S60" s="113"/>
-      <c r="T60" s="115"/>
-      <c r="U60" s="115" t="str">
+      <c r="T60" s="113"/>
+      <c r="U60" s="113" t="str">
         <f t="shared" si="9"/>
         <v>t-dis-clvssrap01-nic</v>
       </c>
@@ -16164,10 +16141,10 @@
         <v>198</v>
       </c>
       <c r="Y60" s="113" t="s">
-        <v>591</v>
+        <v>450</v>
       </c>
       <c r="Z60" s="113" t="s">
-        <v>593</v>
+        <v>590</v>
       </c>
       <c r="AA60" s="107" t="b">
         <v>1</v>
@@ -16192,7 +16169,7 @@
         <f t="array" ref="C61">UPPER(INDEX(_xlfn.TEXTSPLIT($D61, "-"), 3))</f>
         <v>DIS</v>
       </c>
-      <c r="D61" s="115" t="s">
+      <c r="D61" s="113" t="s">
         <v>577</v>
       </c>
       <c r="E61" s="113" t="s">
@@ -16204,7 +16181,7 @@
       <c r="G61" s="113" t="s">
         <v>587</v>
       </c>
-      <c r="H61" s="116" t="s">
+      <c r="H61" s="114" t="s">
         <v>179</v>
       </c>
       <c r="I61" s="113">
@@ -16225,7 +16202,7 @@
       <c r="N61" s="110" t="s">
         <v>584</v>
       </c>
-      <c r="O61" s="115" t="str">
+      <c r="O61" s="113" t="str">
         <f t="shared" si="8"/>
         <v>t-dis-clvadmweb01-osdisk</v>
       </c>
@@ -16235,10 +16212,10 @@
       <c r="Q61" s="107" t="s">
         <v>181</v>
       </c>
-      <c r="R61" s="115"/>
+      <c r="R61" s="113"/>
       <c r="S61" s="113"/>
-      <c r="T61" s="115"/>
-      <c r="U61" s="115" t="str">
+      <c r="T61" s="113"/>
+      <c r="U61" s="113" t="str">
         <f t="shared" si="9"/>
         <v>t-dis-clvadmweb01-nic</v>
       </c>
@@ -16252,10 +16229,10 @@
         <v>198</v>
       </c>
       <c r="Y61" s="113" t="s">
+        <v>450</v>
+      </c>
+      <c r="Z61" s="113" t="s">
         <v>590</v>
-      </c>
-      <c r="Z61" s="113" t="s">
-        <v>593</v>
       </c>
       <c r="AA61" s="107" t="b">
         <v>1</v>
@@ -16280,7 +16257,7 @@
         <f t="array" ref="C62">UPPER(INDEX(_xlfn.TEXTSPLIT($D62, "-"), 3))</f>
         <v>DIS</v>
       </c>
-      <c r="D62" s="114" t="s">
+      <c r="D62" s="107" t="s">
         <v>577</v>
       </c>
       <c r="E62" s="113" t="s">
@@ -16292,7 +16269,7 @@
       <c r="G62" s="113" t="s">
         <v>588</v>
       </c>
-      <c r="H62" s="116" t="s">
+      <c r="H62" s="114" t="s">
         <v>179</v>
       </c>
       <c r="I62" s="107">
@@ -16313,7 +16290,7 @@
       <c r="N62" s="111" t="s">
         <v>584</v>
       </c>
-      <c r="O62" s="115" t="str">
+      <c r="O62" s="113" t="str">
         <f t="shared" si="8"/>
         <v>t-dis-clvadmap01-osdisk</v>
       </c>
@@ -16323,10 +16300,10 @@
       <c r="Q62" s="107" t="s">
         <v>181</v>
       </c>
-      <c r="R62" s="115"/>
+      <c r="R62" s="113"/>
       <c r="S62" s="113"/>
-      <c r="T62" s="115"/>
-      <c r="U62" s="115" t="str">
+      <c r="T62" s="113"/>
+      <c r="U62" s="113" t="str">
         <f t="shared" si="9"/>
         <v>t-dis-clvadmap01-nic</v>
       </c>
@@ -16340,10 +16317,10 @@
         <v>198</v>
       </c>
       <c r="Y62" s="113" t="s">
+        <v>450</v>
+      </c>
+      <c r="Z62" s="113" t="s">
         <v>590</v>
-      </c>
-      <c r="Z62" s="113" t="s">
-        <v>593</v>
       </c>
       <c r="AA62" s="107" t="b">
         <v>1</v>
@@ -19543,7 +19520,7 @@
         <v>24</v>
       </c>
       <c r="F58" s="74" t="s">
-        <v>594</v>
+        <v>591</v>
       </c>
       <c r="G58" s="74" t="str">
         <f t="shared" si="4"/>
@@ -19597,7 +19574,7 @@
         <v>24</v>
       </c>
       <c r="F59" s="73" t="s">
-        <v>595</v>
+        <v>592</v>
       </c>
       <c r="G59" s="73" t="str">
         <f t="shared" si="4"/>
@@ -19651,7 +19628,7 @@
         <v>24</v>
       </c>
       <c r="F60" s="74" t="s">
-        <v>596</v>
+        <v>593</v>
       </c>
       <c r="G60" s="74" t="str">
         <f t="shared" si="4"/>
@@ -19705,7 +19682,7 @@
         <v>24</v>
       </c>
       <c r="F61" s="73" t="s">
-        <v>597</v>
+        <v>594</v>
       </c>
       <c r="G61" s="73" t="str">
         <f t="shared" si="4"/>
@@ -19759,7 +19736,7 @@
         <v>24</v>
       </c>
       <c r="F62" s="74" t="s">
-        <v>598</v>
+        <v>595</v>
       </c>
       <c r="G62" s="74" t="str">
         <f t="shared" si="4"/>
@@ -22731,7 +22708,7 @@
         <v>290</v>
       </c>
       <c r="I76" s="82" t="s">
-        <v>594</v>
+        <v>591</v>
       </c>
       <c r="J76" s="82" t="s">
         <v>286</v>
@@ -22770,7 +22747,7 @@
         <v>288</v>
       </c>
       <c r="I77" s="80" t="s">
-        <v>595</v>
+        <v>592</v>
       </c>
       <c r="J77" s="80" t="s">
         <v>286</v>
@@ -22805,11 +22782,11 @@
       <c r="G78" s="82" t="s">
         <v>200</v>
       </c>
-      <c r="H78" s="117" t="s">
+      <c r="H78" s="82" t="s">
         <v>288</v>
       </c>
       <c r="I78" s="82" t="s">
-        <v>596</v>
+        <v>593</v>
       </c>
       <c r="J78" s="82" t="s">
         <v>286</v>
@@ -22848,7 +22825,7 @@
         <v>288</v>
       </c>
       <c r="I79" s="80" t="s">
-        <v>597</v>
+        <v>594</v>
       </c>
       <c r="J79" s="80" t="s">
         <v>286</v>
@@ -22883,11 +22860,11 @@
       <c r="G80" s="82" t="s">
         <v>200</v>
       </c>
-      <c r="H80" s="117" t="s">
+      <c r="H80" s="82" t="s">
         <v>288</v>
       </c>
       <c r="I80" s="82" t="s">
-        <v>598</v>
+        <v>595</v>
       </c>
       <c r="J80" s="82" t="s">
         <v>286</v>
@@ -27540,7 +27517,7 @@
         <v>24</v>
       </c>
       <c r="F41" s="84" t="s">
-        <v>599</v>
+        <v>596</v>
       </c>
       <c r="G41" s="84" t="s">
         <v>111</v>
@@ -27571,7 +27548,7 @@
         <v>108</v>
       </c>
       <c r="P41" s="84" t="s">
-        <v>600</v>
+        <v>597</v>
       </c>
       <c r="Q41" s="85" t="str">
         <f t="shared" si="5"/>
@@ -27593,7 +27570,7 @@
         <v>24</v>
       </c>
       <c r="F42" s="74" t="s">
-        <v>601</v>
+        <v>598</v>
       </c>
       <c r="G42" s="74" t="s">
         <v>111</v>
@@ -27624,7 +27601,7 @@
         <v>108</v>
       </c>
       <c r="P42" s="74" t="s">
-        <v>602</v>
+        <v>599</v>
       </c>
       <c r="Q42" s="87" t="str">
         <f t="shared" si="5"/>
@@ -27646,7 +27623,7 @@
         <v>24</v>
       </c>
       <c r="F43" s="84" t="s">
-        <v>603</v>
+        <v>600</v>
       </c>
       <c r="G43" s="84" t="s">
         <v>111</v>
@@ -27677,7 +27654,7 @@
         <v>108</v>
       </c>
       <c r="P43" s="84" t="s">
-        <v>604</v>
+        <v>601</v>
       </c>
       <c r="Q43" s="85" t="str">
         <f t="shared" si="5"/>
@@ -27699,7 +27676,7 @@
         <v>24</v>
       </c>
       <c r="F44" s="74" t="s">
-        <v>605</v>
+        <v>602</v>
       </c>
       <c r="G44" s="74" t="s">
         <v>111</v>
@@ -27730,7 +27707,7 @@
         <v>108</v>
       </c>
       <c r="P44" s="74" t="s">
-        <v>606</v>
+        <v>603</v>
       </c>
       <c r="Q44" s="87" t="str">
         <f t="shared" si="5"/>
@@ -27752,7 +27729,7 @@
         <v>24</v>
       </c>
       <c r="F45" s="84" t="s">
-        <v>607</v>
+        <v>604</v>
       </c>
       <c r="G45" s="84" t="s">
         <v>111</v>
@@ -27783,7 +27760,7 @@
         <v>108</v>
       </c>
       <c r="P45" s="84" t="s">
-        <v>608</v>
+        <v>605</v>
       </c>
       <c r="Q45" s="85" t="str">
         <f t="shared" si="5"/>
@@ -29665,7 +29642,6 @@
       </c>
     </row>
     <row r="58" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A58" s="118"/>
       <c r="B58" s="84" t="s">
         <v>567</v>
       </c>
@@ -29693,7 +29669,6 @@
       </c>
     </row>
     <row r="59" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A59" s="118"/>
       <c r="B59" s="74" t="s">
         <v>182</v>
       </c>
@@ -29732,14 +29707,14 @@
         <v>286</v>
       </c>
       <c r="E60" s="84" t="s">
-        <v>599</v>
+        <v>596</v>
       </c>
       <c r="F60" s="84" t="str">
         <f t="shared" si="5"/>
         <v>t-dis-clvweb-lb-pb443</v>
       </c>
       <c r="G60" s="84" t="s">
-        <v>609</v>
+        <v>606</v>
       </c>
       <c r="H60" s="84">
         <v>443</v>
@@ -29764,14 +29739,14 @@
         <v>286</v>
       </c>
       <c r="E61" s="74" t="s">
-        <v>601</v>
+        <v>598</v>
       </c>
       <c r="F61" s="74" t="str">
         <f t="shared" si="6"/>
         <v>t-dis-clvap-lb-pb8080</v>
       </c>
       <c r="G61" s="74" t="s">
-        <v>609</v>
+        <v>606</v>
       </c>
       <c r="H61" s="74">
         <v>8080</v>
@@ -29796,14 +29771,14 @@
         <v>286</v>
       </c>
       <c r="E62" s="84" t="s">
-        <v>603</v>
+        <v>600</v>
       </c>
       <c r="F62" s="84" t="str">
         <f t="shared" si="5"/>
         <v>t-dis-clvssrap-lb-pb8080</v>
       </c>
       <c r="G62" s="84" t="s">
-        <v>609</v>
+        <v>606</v>
       </c>
       <c r="H62" s="84">
         <v>8080</v>
@@ -29828,14 +29803,14 @@
         <v>286</v>
       </c>
       <c r="E63" s="74" t="s">
-        <v>605</v>
+        <v>602</v>
       </c>
       <c r="F63" s="74" t="str">
         <f t="shared" si="6"/>
         <v>t-dis-clvadmweb-lb-pb443</v>
       </c>
       <c r="G63" s="74" t="s">
-        <v>609</v>
+        <v>606</v>
       </c>
       <c r="H63" s="74">
         <v>443</v>
@@ -29860,14 +29835,14 @@
         <v>286</v>
       </c>
       <c r="E64" s="84" t="s">
-        <v>607</v>
+        <v>604</v>
       </c>
       <c r="F64" s="84" t="str">
         <f t="shared" si="5"/>
         <v>t-dis-clvadmap-lb-pb8080</v>
       </c>
       <c r="G64" s="84" t="s">
-        <v>609</v>
+        <v>606</v>
       </c>
       <c r="H64" s="84">
         <v>8080</v>
@@ -29887,21 +29862,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
-</p:properties>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="문서" ma:contentTypeID="0x010100589F7F6AEE51BC4C92024CB999111E60" ma:contentTypeVersion="4" ma:contentTypeDescription="새 문서를 만듭니다." ma:contentTypeScope="" ma:versionID="7236b106e1291626cb10ba6ee71a9b94">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="89f0f392-688b-4454-b192-0691f37dc811" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="39d8cc4ddeff20ae29b23e47bf838372" ns2:_="">
     <xsd:import namespace="89f0f392-688b-4454-b192-0691f37dc811"/>
@@ -30045,31 +30005,22 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BF093BAC-4385-48E8-8492-BA8C8E7EF612}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="89f0f392-688b-4454-b192-0691f37dc811"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CAFDA824-0F2E-4C40-8FCD-BF3D34EF26B3}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
 </file>
 
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B942A36D-0DEC-4379-B834-CD4D85F3BBDA}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -30085,4 +30036,28 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CAFDA824-0F2E-4C40-8FCD-BF3D34EF26B3}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BF093BAC-4385-48E8-8492-BA8C8E7EF612}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="89f0f392-688b-4454-b192-0691f37dc811"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
--- a/서버정보/20260911_리소스배포_테스트.xlsx
+++ b/서버정보/20260911_리소스배포_테스트.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\zenithn\PowerShell - 리소스 배포\서버정보\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{705B20C8-B990-4860-91B9-03F8563A8324}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FA737D75-07B6-4CC8-A1EB-107C3D997B87}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="VNET" sheetId="4" r:id="rId1"/>
@@ -1659,7 +1659,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4207" uniqueCount="607">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4204" uniqueCount="606">
   <si>
     <t>Stage</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -3727,10 +3727,6 @@
   </si>
   <si>
     <t>D8s_v5</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>TREU</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -10160,17 +10156,17 @@
     </row>
     <row r="58" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A58" s="84" t="s">
-        <v>567</v>
+        <v>566</v>
       </c>
       <c r="B58" s="84" t="str" cm="1">
         <f t="array" ref="B58">UPPER(INDEX(_xlfn.TEXTSPLIT($C58, "-"), 3))</f>
         <v>BDP</v>
       </c>
       <c r="C58" s="84" t="s">
-        <v>572</v>
+        <v>571</v>
       </c>
       <c r="D58" s="84" t="s">
-        <v>568</v>
+        <v>567</v>
       </c>
       <c r="E58" s="84" t="str">
         <f t="shared" si="24"/>
@@ -10181,7 +10177,7 @@
         <v>t-bdp-rlgcweb-lb-fe</v>
       </c>
       <c r="G58" s="84" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
       <c r="H58" s="84"/>
       <c r="I58" s="84" t="b">
@@ -10197,14 +10193,14 @@
         <v>t-bdp-rlgcweb-lb-pb</v>
       </c>
       <c r="M58" s="84" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
       <c r="N58" s="84"/>
       <c r="O58" s="84">
         <v>4</v>
       </c>
       <c r="P58" s="84" t="s">
-        <v>574</v>
+        <v>573</v>
       </c>
       <c r="Q58" s="84" t="b">
         <v>1</v>
@@ -10225,7 +10221,7 @@
         <v>375</v>
       </c>
       <c r="D59" s="74" t="s">
-        <v>569</v>
+        <v>568</v>
       </c>
       <c r="E59" s="74" t="str">
         <f t="shared" ref="E59:E63" si="28">SUBSTITUTE(D59, "hazr-", "")&amp;"-rule"&amp;N59</f>
@@ -10280,7 +10276,7 @@
         <v>286</v>
       </c>
       <c r="D60" s="84" t="s">
-        <v>596</v>
+        <v>595</v>
       </c>
       <c r="E60" s="84" t="str">
         <f t="shared" si="24"/>
@@ -10341,7 +10337,7 @@
         <v>286</v>
       </c>
       <c r="D61" s="74" t="s">
-        <v>598</v>
+        <v>597</v>
       </c>
       <c r="E61" s="74" t="str">
         <f t="shared" si="28"/>
@@ -10402,7 +10398,7 @@
         <v>286</v>
       </c>
       <c r="D62" s="84" t="s">
-        <v>600</v>
+        <v>599</v>
       </c>
       <c r="E62" s="84" t="str">
         <f t="shared" si="24"/>
@@ -10463,7 +10459,7 @@
         <v>286</v>
       </c>
       <c r="D63" s="74" t="s">
-        <v>602</v>
+        <v>601</v>
       </c>
       <c r="E63" s="74" t="str">
         <f t="shared" si="28"/>
@@ -10524,7 +10520,7 @@
         <v>286</v>
       </c>
       <c r="D64" s="84" t="s">
-        <v>604</v>
+        <v>603</v>
       </c>
       <c r="E64" s="84" t="str">
         <f t="shared" si="24"/>
@@ -15759,7 +15755,7 @@
         <v>521</v>
       </c>
       <c r="N56" s="111" t="s">
-        <v>575</v>
+        <v>574</v>
       </c>
       <c r="O56" s="107" t="str">
         <f>SUBSTITUTE(F56,"hazr-","")&amp;"-osdisk"</f>
@@ -15848,7 +15844,7 @@
         <v>521</v>
       </c>
       <c r="N57" s="111" t="s">
-        <v>575</v>
+        <v>574</v>
       </c>
       <c r="O57" s="107" t="str">
         <f>SUBSTITUTE(F57,"hazr-","")&amp;"-osdisk"</f>
@@ -15867,8 +15863,8 @@
         <f t="shared" si="7"/>
         <v>t-bdp-rlgcap01-nic</v>
       </c>
-      <c r="V57" s="107" t="s">
-        <v>565</v>
+      <c r="V57" s="107" t="b">
+        <v>1</v>
       </c>
       <c r="W57" s="107" t="b">
         <v>1</v>
@@ -15899,23 +15895,23 @@
     </row>
     <row r="58" spans="1:32" x14ac:dyDescent="0.3">
       <c r="B58" s="107" t="s">
-        <v>576</v>
+        <v>575</v>
       </c>
       <c r="C58" s="107" t="str" cm="1">
         <f t="array" ref="C58">UPPER(INDEX(_xlfn.TEXTSPLIT($D58, "-"), 3))</f>
         <v>DIS</v>
       </c>
       <c r="D58" s="107" t="s">
-        <v>577</v>
+        <v>576</v>
       </c>
       <c r="E58" s="107" t="s">
         <v>24</v>
       </c>
       <c r="F58" s="107" t="s">
-        <v>578</v>
+        <v>577</v>
       </c>
       <c r="G58" s="107" t="s">
-        <v>583</v>
+        <v>582</v>
       </c>
       <c r="H58" s="108" t="s">
         <v>179</v>
@@ -15936,7 +15932,7 @@
         <v>521</v>
       </c>
       <c r="N58" s="110" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="O58" s="107" t="str">
         <f t="shared" ref="O58:O62" si="8">SUBSTITUTE(F58,"hazr-","")&amp;"-osdisk"</f>
@@ -15968,7 +15964,7 @@
         <v>451</v>
       </c>
       <c r="Z58" s="107" t="s">
-        <v>589</v>
+        <v>588</v>
       </c>
       <c r="AA58" s="107" t="b">
         <v>1</v>
@@ -15987,23 +15983,23 @@
     </row>
     <row r="59" spans="1:32" x14ac:dyDescent="0.3">
       <c r="B59" s="113" t="s">
-        <v>576</v>
+        <v>575</v>
       </c>
       <c r="C59" s="107" t="str" cm="1">
         <f t="array" ref="C59">UPPER(INDEX(_xlfn.TEXTSPLIT($D59, "-"), 3))</f>
         <v>DIS</v>
       </c>
       <c r="D59" s="113" t="s">
-        <v>577</v>
+        <v>576</v>
       </c>
       <c r="E59" s="113" t="s">
         <v>24</v>
       </c>
       <c r="F59" s="113" t="s">
-        <v>579</v>
+        <v>578</v>
       </c>
       <c r="G59" s="113" t="s">
-        <v>585</v>
+        <v>584</v>
       </c>
       <c r="H59" s="114" t="s">
         <v>179</v>
@@ -16024,7 +16020,7 @@
         <v>521</v>
       </c>
       <c r="N59" s="110" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="O59" s="113" t="str">
         <f t="shared" si="8"/>
@@ -16043,8 +16039,8 @@
         <f t="shared" si="9"/>
         <v>t-dis-clvap01-nic</v>
       </c>
-      <c r="V59" s="107" t="s">
-        <v>565</v>
+      <c r="V59" s="107" t="b">
+        <v>1</v>
       </c>
       <c r="W59" s="107" t="b">
         <v>1</v>
@@ -16056,7 +16052,7 @@
         <v>450</v>
       </c>
       <c r="Z59" s="113" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
       <c r="AA59" s="107" t="b">
         <v>1</v>
@@ -16075,23 +16071,23 @@
     </row>
     <row r="60" spans="1:32" x14ac:dyDescent="0.3">
       <c r="B60" s="113" t="s">
-        <v>576</v>
+        <v>575</v>
       </c>
       <c r="C60" s="107" t="str" cm="1">
         <f t="array" ref="C60">UPPER(INDEX(_xlfn.TEXTSPLIT($D60, "-"), 3))</f>
         <v>DIS</v>
       </c>
       <c r="D60" s="107" t="s">
-        <v>577</v>
+        <v>576</v>
       </c>
       <c r="E60" s="113" t="s">
         <v>24</v>
       </c>
       <c r="F60" s="113" t="s">
-        <v>580</v>
+        <v>579</v>
       </c>
       <c r="G60" s="113" t="s">
-        <v>586</v>
+        <v>585</v>
       </c>
       <c r="H60" s="114" t="s">
         <v>179</v>
@@ -16112,7 +16108,7 @@
         <v>521</v>
       </c>
       <c r="N60" s="110" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="O60" s="113" t="str">
         <f t="shared" si="8"/>
@@ -16144,7 +16140,7 @@
         <v>450</v>
       </c>
       <c r="Z60" s="113" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
       <c r="AA60" s="107" t="b">
         <v>1</v>
@@ -16163,23 +16159,23 @@
     </row>
     <row r="61" spans="1:32" x14ac:dyDescent="0.3">
       <c r="B61" s="113" t="s">
-        <v>576</v>
+        <v>575</v>
       </c>
       <c r="C61" s="107" t="str" cm="1">
         <f t="array" ref="C61">UPPER(INDEX(_xlfn.TEXTSPLIT($D61, "-"), 3))</f>
         <v>DIS</v>
       </c>
       <c r="D61" s="113" t="s">
-        <v>577</v>
+        <v>576</v>
       </c>
       <c r="E61" s="113" t="s">
         <v>24</v>
       </c>
       <c r="F61" s="113" t="s">
-        <v>581</v>
+        <v>580</v>
       </c>
       <c r="G61" s="113" t="s">
-        <v>587</v>
+        <v>586</v>
       </c>
       <c r="H61" s="114" t="s">
         <v>179</v>
@@ -16200,7 +16196,7 @@
         <v>521</v>
       </c>
       <c r="N61" s="110" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="O61" s="113" t="str">
         <f t="shared" si="8"/>
@@ -16219,8 +16215,8 @@
         <f t="shared" si="9"/>
         <v>t-dis-clvadmweb01-nic</v>
       </c>
-      <c r="V61" s="107" t="s">
-        <v>565</v>
+      <c r="V61" s="107" t="b">
+        <v>1</v>
       </c>
       <c r="W61" s="107" t="b">
         <v>1</v>
@@ -16232,7 +16228,7 @@
         <v>450</v>
       </c>
       <c r="Z61" s="113" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
       <c r="AA61" s="107" t="b">
         <v>1</v>
@@ -16251,23 +16247,23 @@
     </row>
     <row r="62" spans="1:32" x14ac:dyDescent="0.3">
       <c r="B62" s="113" t="s">
-        <v>576</v>
+        <v>575</v>
       </c>
       <c r="C62" s="107" t="str" cm="1">
         <f t="array" ref="C62">UPPER(INDEX(_xlfn.TEXTSPLIT($D62, "-"), 3))</f>
         <v>DIS</v>
       </c>
       <c r="D62" s="107" t="s">
-        <v>577</v>
+        <v>576</v>
       </c>
       <c r="E62" s="113" t="s">
         <v>24</v>
       </c>
       <c r="F62" s="113" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="G62" s="113" t="s">
-        <v>588</v>
+        <v>587</v>
       </c>
       <c r="H62" s="114" t="s">
         <v>179</v>
@@ -16288,7 +16284,7 @@
         <v>521</v>
       </c>
       <c r="N62" s="111" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="O62" s="113" t="str">
         <f t="shared" si="8"/>
@@ -16320,7 +16316,7 @@
         <v>450</v>
       </c>
       <c r="Z62" s="113" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
       <c r="AA62" s="107" t="b">
         <v>1</v>
@@ -19520,7 +19516,7 @@
         <v>24</v>
       </c>
       <c r="F58" s="74" t="s">
-        <v>591</v>
+        <v>590</v>
       </c>
       <c r="G58" s="74" t="str">
         <f t="shared" si="4"/>
@@ -19574,7 +19570,7 @@
         <v>24</v>
       </c>
       <c r="F59" s="73" t="s">
-        <v>592</v>
+        <v>591</v>
       </c>
       <c r="G59" s="73" t="str">
         <f t="shared" si="4"/>
@@ -19628,7 +19624,7 @@
         <v>24</v>
       </c>
       <c r="F60" s="74" t="s">
-        <v>593</v>
+        <v>592</v>
       </c>
       <c r="G60" s="74" t="str">
         <f t="shared" si="4"/>
@@ -19682,7 +19678,7 @@
         <v>24</v>
       </c>
       <c r="F61" s="73" t="s">
-        <v>594</v>
+        <v>593</v>
       </c>
       <c r="G61" s="73" t="str">
         <f t="shared" si="4"/>
@@ -19736,7 +19732,7 @@
         <v>24</v>
       </c>
       <c r="F62" s="74" t="s">
-        <v>595</v>
+        <v>594</v>
       </c>
       <c r="G62" s="74" t="str">
         <f t="shared" si="4"/>
@@ -22639,7 +22635,7 @@
         <v>516</v>
       </c>
       <c r="M74" s="82" t="s">
-        <v>566</v>
+        <v>565</v>
       </c>
     </row>
     <row r="75" spans="1:13" x14ac:dyDescent="0.3">
@@ -22680,7 +22676,7 @@
         <v>516</v>
       </c>
       <c r="M75" s="80" t="s">
-        <v>566</v>
+        <v>565</v>
       </c>
     </row>
     <row r="76" spans="1:13" x14ac:dyDescent="0.3">
@@ -22708,7 +22704,7 @@
         <v>290</v>
       </c>
       <c r="I76" s="82" t="s">
-        <v>591</v>
+        <v>590</v>
       </c>
       <c r="J76" s="82" t="s">
         <v>286</v>
@@ -22747,7 +22743,7 @@
         <v>288</v>
       </c>
       <c r="I77" s="80" t="s">
-        <v>592</v>
+        <v>591</v>
       </c>
       <c r="J77" s="80" t="s">
         <v>286</v>
@@ -22786,7 +22782,7 @@
         <v>288</v>
       </c>
       <c r="I78" s="82" t="s">
-        <v>593</v>
+        <v>592</v>
       </c>
       <c r="J78" s="82" t="s">
         <v>286</v>
@@ -22825,7 +22821,7 @@
         <v>288</v>
       </c>
       <c r="I79" s="80" t="s">
-        <v>594</v>
+        <v>593</v>
       </c>
       <c r="J79" s="80" t="s">
         <v>286</v>
@@ -22864,7 +22860,7 @@
         <v>288</v>
       </c>
       <c r="I80" s="82" t="s">
-        <v>595</v>
+        <v>594</v>
       </c>
       <c r="J80" s="82" t="s">
         <v>286</v>
@@ -27397,7 +27393,7 @@
     <row r="39" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A39" s="97"/>
       <c r="B39" s="84" t="s">
-        <v>567</v>
+        <v>566</v>
       </c>
       <c r="C39" s="84" t="str" cm="1">
         <f t="array" ref="C39">UPPER(INDEX(_xlfn.TEXTSPLIT($F39, "-"), 3))</f>
@@ -27410,7 +27406,7 @@
         <v>24</v>
       </c>
       <c r="F39" s="84" t="s">
-        <v>568</v>
+        <v>567</v>
       </c>
       <c r="G39" s="84" t="s">
         <v>111</v>
@@ -27441,7 +27437,7 @@
         <v>108</v>
       </c>
       <c r="P39" s="84" t="s">
-        <v>570</v>
+        <v>569</v>
       </c>
       <c r="Q39" s="85" t="str">
         <f t="shared" si="3"/>
@@ -27451,7 +27447,7 @@
     <row r="40" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A40" s="97"/>
       <c r="B40" s="74" t="s">
-        <v>567</v>
+        <v>566</v>
       </c>
       <c r="C40" s="74" t="str" cm="1">
         <f t="array" ref="C40">UPPER(INDEX(_xlfn.TEXTSPLIT($F40, "-"), 3))</f>
@@ -27464,7 +27460,7 @@
         <v>24</v>
       </c>
       <c r="F40" s="74" t="s">
-        <v>569</v>
+        <v>568</v>
       </c>
       <c r="G40" s="74" t="s">
         <v>111</v>
@@ -27495,7 +27491,7 @@
         <v>108</v>
       </c>
       <c r="P40" s="74" t="s">
-        <v>571</v>
+        <v>570</v>
       </c>
       <c r="Q40" s="87" t="str">
         <f t="shared" ref="Q40:Q45" si="5">SUBSTITUTE(F40, "hazr-", "")&amp;"-bp"</f>
@@ -27517,7 +27513,7 @@
         <v>24</v>
       </c>
       <c r="F41" s="84" t="s">
-        <v>596</v>
+        <v>595</v>
       </c>
       <c r="G41" s="84" t="s">
         <v>111</v>
@@ -27548,7 +27544,7 @@
         <v>108</v>
       </c>
       <c r="P41" s="84" t="s">
-        <v>597</v>
+        <v>596</v>
       </c>
       <c r="Q41" s="85" t="str">
         <f t="shared" si="5"/>
@@ -27570,7 +27566,7 @@
         <v>24</v>
       </c>
       <c r="F42" s="74" t="s">
-        <v>598</v>
+        <v>597</v>
       </c>
       <c r="G42" s="74" t="s">
         <v>111</v>
@@ -27601,7 +27597,7 @@
         <v>108</v>
       </c>
       <c r="P42" s="74" t="s">
-        <v>599</v>
+        <v>598</v>
       </c>
       <c r="Q42" s="87" t="str">
         <f t="shared" si="5"/>
@@ -27623,7 +27619,7 @@
         <v>24</v>
       </c>
       <c r="F43" s="84" t="s">
-        <v>600</v>
+        <v>599</v>
       </c>
       <c r="G43" s="84" t="s">
         <v>111</v>
@@ -27654,7 +27650,7 @@
         <v>108</v>
       </c>
       <c r="P43" s="84" t="s">
-        <v>601</v>
+        <v>600</v>
       </c>
       <c r="Q43" s="85" t="str">
         <f t="shared" si="5"/>
@@ -27676,7 +27672,7 @@
         <v>24</v>
       </c>
       <c r="F44" s="74" t="s">
-        <v>602</v>
+        <v>601</v>
       </c>
       <c r="G44" s="74" t="s">
         <v>111</v>
@@ -27707,7 +27703,7 @@
         <v>108</v>
       </c>
       <c r="P44" s="74" t="s">
-        <v>603</v>
+        <v>602</v>
       </c>
       <c r="Q44" s="87" t="str">
         <f t="shared" si="5"/>
@@ -27729,7 +27725,7 @@
         <v>24</v>
       </c>
       <c r="F45" s="84" t="s">
-        <v>604</v>
+        <v>603</v>
       </c>
       <c r="G45" s="84" t="s">
         <v>111</v>
@@ -27760,7 +27756,7 @@
         <v>108</v>
       </c>
       <c r="P45" s="84" t="s">
-        <v>605</v>
+        <v>604</v>
       </c>
       <c r="Q45" s="85" t="str">
         <f t="shared" si="5"/>
@@ -29643,21 +29639,21 @@
     </row>
     <row r="58" spans="1:11" x14ac:dyDescent="0.3">
       <c r="B58" s="84" t="s">
-        <v>567</v>
+        <v>566</v>
       </c>
       <c r="C58" s="84" t="str" cm="1">
         <f t="array" ref="C58">UPPER(INDEX(_xlfn.TEXTSPLIT($D58, "-"), 3))</f>
         <v>BDP</v>
       </c>
       <c r="D58" s="84" t="s">
-        <v>572</v>
+        <v>571</v>
       </c>
       <c r="E58" s="84" t="s">
-        <v>568</v>
+        <v>567</v>
       </c>
       <c r="F58" s="84"/>
       <c r="G58" s="84" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
       <c r="H58" s="84"/>
       <c r="I58" s="84"/>
@@ -29680,7 +29676,7 @@
         <v>375</v>
       </c>
       <c r="E59" s="74" t="s">
-        <v>569</v>
+        <v>568</v>
       </c>
       <c r="F59" s="74"/>
       <c r="G59" s="74" t="s">
@@ -29707,14 +29703,14 @@
         <v>286</v>
       </c>
       <c r="E60" s="84" t="s">
-        <v>596</v>
+        <v>595</v>
       </c>
       <c r="F60" s="84" t="str">
         <f t="shared" si="5"/>
         <v>t-dis-clvweb-lb-pb443</v>
       </c>
       <c r="G60" s="84" t="s">
-        <v>606</v>
+        <v>605</v>
       </c>
       <c r="H60" s="84">
         <v>443</v>
@@ -29739,14 +29735,14 @@
         <v>286</v>
       </c>
       <c r="E61" s="74" t="s">
-        <v>598</v>
+        <v>597</v>
       </c>
       <c r="F61" s="74" t="str">
         <f t="shared" si="6"/>
         <v>t-dis-clvap-lb-pb8080</v>
       </c>
       <c r="G61" s="74" t="s">
-        <v>606</v>
+        <v>605</v>
       </c>
       <c r="H61" s="74">
         <v>8080</v>
@@ -29771,14 +29767,14 @@
         <v>286</v>
       </c>
       <c r="E62" s="84" t="s">
-        <v>600</v>
+        <v>599</v>
       </c>
       <c r="F62" s="84" t="str">
         <f t="shared" si="5"/>
         <v>t-dis-clvssrap-lb-pb8080</v>
       </c>
       <c r="G62" s="84" t="s">
-        <v>606</v>
+        <v>605</v>
       </c>
       <c r="H62" s="84">
         <v>8080</v>
@@ -29803,14 +29799,14 @@
         <v>286</v>
       </c>
       <c r="E63" s="74" t="s">
-        <v>602</v>
+        <v>601</v>
       </c>
       <c r="F63" s="74" t="str">
         <f t="shared" si="6"/>
         <v>t-dis-clvadmweb-lb-pb443</v>
       </c>
       <c r="G63" s="74" t="s">
-        <v>606</v>
+        <v>605</v>
       </c>
       <c r="H63" s="74">
         <v>443</v>
@@ -29835,14 +29831,14 @@
         <v>286</v>
       </c>
       <c r="E64" s="84" t="s">
-        <v>604</v>
+        <v>603</v>
       </c>
       <c r="F64" s="84" t="str">
         <f t="shared" si="5"/>
         <v>t-dis-clvadmap-lb-pb8080</v>
       </c>
       <c r="G64" s="84" t="s">
-        <v>606</v>
+        <v>605</v>
       </c>
       <c r="H64" s="84">
         <v>8080</v>
@@ -29862,6 +29858,21 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="문서" ma:contentTypeID="0x010100589F7F6AEE51BC4C92024CB999111E60" ma:contentTypeVersion="4" ma:contentTypeDescription="새 문서를 만듭니다." ma:contentTypeScope="" ma:versionID="7236b106e1291626cb10ba6ee71a9b94">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="89f0f392-688b-4454-b192-0691f37dc811" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="39d8cc4ddeff20ae29b23e47bf838372" ns2:_="">
     <xsd:import namespace="89f0f392-688b-4454-b192-0691f37dc811"/>
@@ -30005,22 +30016,31 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BF093BAC-4385-48E8-8492-BA8C8E7EF612}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="89f0f392-688b-4454-b192-0691f37dc811"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
-</p:properties>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CAFDA824-0F2E-4C40-8FCD-BF3D34EF26B3}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B942A36D-0DEC-4379-B834-CD4D85F3BBDA}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -30036,28 +30056,4 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CAFDA824-0F2E-4C40-8FCD-BF3D34EF26B3}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BF093BAC-4385-48E8-8492-BA8C8E7EF612}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="89f0f392-688b-4454-b192-0691f37dc811"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/서버정보/20260911_리소스배포_테스트.xlsx
+++ b/서버정보/20260911_리소스배포_테스트.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\zenithn\PowerShell - 리소스 배포\서버정보\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FA737D75-07B6-4CC8-A1EB-107C3D997B87}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C9DE333D-7144-447A-B2CF-D1CB4617C95A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -19526,7 +19526,7 @@
         <v>181</v>
       </c>
       <c r="I58" s="74">
-        <v>64</v>
+        <v>128</v>
       </c>
       <c r="J58" s="74" t="str">
         <f t="shared" si="5"/>
@@ -19536,7 +19536,7 @@
         <v>181</v>
       </c>
       <c r="L58" s="74">
-        <v>64</v>
+        <v>128</v>
       </c>
       <c r="M58" s="74">
         <v>3</v>
@@ -19580,7 +19580,7 @@
         <v>181</v>
       </c>
       <c r="I59" s="73">
-        <v>64</v>
+        <v>128</v>
       </c>
       <c r="J59" s="73" t="str">
         <f t="shared" si="5"/>
@@ -19590,7 +19590,7 @@
         <v>181</v>
       </c>
       <c r="L59" s="73">
-        <v>64</v>
+        <v>128</v>
       </c>
       <c r="M59" s="73">
         <v>3</v>
@@ -19634,7 +19634,7 @@
         <v>181</v>
       </c>
       <c r="I60" s="74">
-        <v>64</v>
+        <v>128</v>
       </c>
       <c r="J60" s="74" t="str">
         <f t="shared" si="5"/>
@@ -19644,7 +19644,7 @@
         <v>181</v>
       </c>
       <c r="L60" s="74">
-        <v>64</v>
+        <v>128</v>
       </c>
       <c r="M60" s="74">
         <v>3</v>
@@ -19688,7 +19688,7 @@
         <v>181</v>
       </c>
       <c r="I61" s="73">
-        <v>64</v>
+        <v>128</v>
       </c>
       <c r="J61" s="73" t="str">
         <f t="shared" si="5"/>
@@ -19698,7 +19698,7 @@
         <v>181</v>
       </c>
       <c r="L61" s="73">
-        <v>64</v>
+        <v>128</v>
       </c>
       <c r="M61" s="73">
         <v>3</v>
@@ -19742,7 +19742,7 @@
         <v>181</v>
       </c>
       <c r="I62" s="74">
-        <v>64</v>
+        <v>128</v>
       </c>
       <c r="J62" s="74" t="str">
         <f t="shared" si="5"/>
@@ -19752,7 +19752,7 @@
         <v>181</v>
       </c>
       <c r="L62" s="74">
-        <v>64</v>
+        <v>128</v>
       </c>
       <c r="M62" s="74">
         <v>3</v>
@@ -29858,21 +29858,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
-</p:properties>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="문서" ma:contentTypeID="0x010100589F7F6AEE51BC4C92024CB999111E60" ma:contentTypeVersion="4" ma:contentTypeDescription="새 문서를 만듭니다." ma:contentTypeScope="" ma:versionID="7236b106e1291626cb10ba6ee71a9b94">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="89f0f392-688b-4454-b192-0691f37dc811" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="39d8cc4ddeff20ae29b23e47bf838372" ns2:_="">
     <xsd:import namespace="89f0f392-688b-4454-b192-0691f37dc811"/>
@@ -30016,31 +30001,22 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BF093BAC-4385-48E8-8492-BA8C8E7EF612}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="89f0f392-688b-4454-b192-0691f37dc811"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CAFDA824-0F2E-4C40-8FCD-BF3D34EF26B3}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
 </file>
 
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B942A36D-0DEC-4379-B834-CD4D85F3BBDA}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -30056,4 +30032,28 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CAFDA824-0F2E-4C40-8FCD-BF3D34EF26B3}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BF093BAC-4385-48E8-8492-BA8C8E7EF612}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="89f0f392-688b-4454-b192-0691f37dc811"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>